--- a/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/01_pos_va_doi_soat.xlsx
+++ b/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/01_pos_va_doi_soat.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R07cfb7243d374102"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" r:id="R6fd8f8622bae4877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payouts" sheetId="3" r:id="Rf9e2883d12e24d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tips" sheetId="4" r:id="Rfeabf83bb31241bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R722f2e9d4eaa4d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" r:id="R85305f06f5b34ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payouts" sheetId="3" r:id="Ra31fe7e4b167493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tips" sheetId="4" r:id="Rb4b20fd329d34432"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/01_pos_va_doi_soat.xlsx
+++ b/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/01_pos_va_doi_soat.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R722f2e9d4eaa4d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" r:id="R85305f06f5b34ee7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payouts" sheetId="3" r:id="Ra31fe7e4b167493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tips" sheetId="4" r:id="Rb4b20fd329d34432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R2ab4bbf6546449eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" r:id="Rd83a4168a2094d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payouts" sheetId="3" r:id="R20807de26fac46c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tips" sheetId="4" r:id="R4026752722a3484a"/>
   </x:sheets>
 </x:workbook>
 </file>
